--- a/VitalSigns/NordicTXTestBuild/ValueSet-NoDomainVitalSignsHeartRateMeasurementMethodValueSet.xlsx
+++ b/VitalSigns/NordicTXTestBuild/ValueSet-NoDomainVitalSignsHeartRateMeasurementMethodValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T07:45:23+00:00</t>
+    <t>2025-11-20T10:22:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
